--- a/Result/09-26-25/NASDAQstock_09-26-25period252RS90.xlsx
+++ b/Result/09-26-25/NASDAQstock_09-26-25period252RS90.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding Project/StockAnalysis/Result/09-26-25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719A46A7-B1F0-664E-A07B-3EB5F9049FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFBD1EA-06E9-184A-A3EF-03D8DBE9E7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
